--- a/SCE_mean_lt.xlsx
+++ b/SCE_mean_lt.xlsx
@@ -69,7 +69,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -387,7 +387,7 @@
         <v>42156</v>
       </c>
       <c r="B31" s="2">
-        <v>4.7730450023916937</v>
+        <v>4.773045002391668</v>
       </c>
       <c r="C31" s="2">
         <v>4</v>
@@ -695,7 +695,7 @@
         <v>43009</v>
       </c>
       <c r="B59" s="2">
-        <v>4.7041640267550529</v>
+        <v>4.704164026755052</v>
       </c>
       <c r="C59" s="2">
         <v>3</v>
@@ -1245,7 +1245,7 @@
         <v>44531</v>
       </c>
       <c r="B109" s="2">
-        <v>4.1201896291367905</v>
+        <v>4.1201896291367914</v>
       </c>
       <c r="C109" s="2">
         <v>4</v>
@@ -1366,7 +1366,7 @@
         <v>44866</v>
       </c>
       <c r="B120" s="2">
-        <v>1.7585324826803159</v>
+        <v>1.7585324826803148</v>
       </c>
       <c r="C120" s="2">
         <v>5</v>
@@ -1596,64 +1596,156 @@
       <c r="A141" s="1">
         <v>45505</v>
       </c>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
+      <c r="B141" s="2">
+        <v>3.0372531943843528</v>
+      </c>
+      <c r="C141" s="2">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1">
         <v>45536</v>
       </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
+      <c r="B142" s="2">
+        <v>4.3181149855475773</v>
+      </c>
+      <c r="C142" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1">
         <v>45566</v>
       </c>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
+      <c r="B143" s="2">
+        <v>3.2207417031864036</v>
+      </c>
+      <c r="C143" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1">
         <v>45597</v>
       </c>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
+      <c r="B144" s="2">
+        <v>2.6219643923616269</v>
+      </c>
+      <c r="C144" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1">
         <v>45627</v>
       </c>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
+      <c r="B145" s="2">
+        <v>2.2907086717310872</v>
+      </c>
+      <c r="C145" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1">
         <v>45658</v>
       </c>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
+      <c r="B146" s="2">
+        <v>2.4539876476999338</v>
+      </c>
+      <c r="C146" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1">
         <v>45689</v>
       </c>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
+      <c r="B147" s="2">
+        <v>2.3142994598129012</v>
+      </c>
+      <c r="C147" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1">
         <v>45717</v>
       </c>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
+      <c r="B148" s="2">
+        <v>4.6217715733926479</v>
+      </c>
+      <c r="C148" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1">
         <v>45748</v>
       </c>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
+      <c r="B149" s="2">
+        <v>2.7085124919420633</v>
+      </c>
+      <c r="C149" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
     </row>
   </sheetData>
 </worksheet>
